--- a/artfynd/A 6823-2026 artfynd.xlsx
+++ b/artfynd/A 6823-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3342,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131674863</v>
+        <v>135298271</v>
       </c>
       <c r="B28" t="n">
-        <v>111153</v>
+        <v>8460</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3353,37 +3353,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220240</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458920</v>
+        <v>458859</v>
       </c>
       <c r="R28" t="n">
-        <v>6781860</v>
+        <v>6781773</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3407,12 +3412,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3427,15 +3442,233 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135298272</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>458876</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6781809</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131674863</v>
+      </c>
+      <c r="B30" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>458920</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6781860</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6823-2026 artfynd.xlsx
+++ b/artfynd/A 6823-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674775</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674810</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674881</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674882</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674883</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674884</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674885</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674886</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674888</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674889</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1755,6 +1810,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674814</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1860,6 +1920,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674815</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1965,6 +2030,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674816</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674817</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2175,6 +2250,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674818</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2280,6 +2360,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674819</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2385,6 +2470,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674837</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674838</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2595,6 +2690,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674777</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2700,6 +2800,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674778</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2805,6 +2910,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674779</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2910,6 +3020,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674780</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3024,6 +3139,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676697</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3129,6 +3249,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674868</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3234,6 +3359,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674869</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3339,6 +3469,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674871</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3451,6 +3586,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298271</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3572,6 +3712,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298272</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3669,8 +3814,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674863</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 6823-2026 artfynd.xlsx
+++ b/artfynd/A 6823-2026 artfynd.xlsx
@@ -3480,7 +3480,7 @@
         <v>135298271</v>
       </c>
       <c r="B28" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>135298272</v>
       </c>
       <c r="B29" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 6823-2026 artfynd.xlsx
+++ b/artfynd/A 6823-2026 artfynd.xlsx
@@ -3597,7 +3597,7 @@
         <v>135298272</v>
       </c>
       <c r="B29" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 6823-2026 artfynd.xlsx
+++ b/artfynd/A 6823-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3477,10 +3477,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131674863</v>
+        <v>135298271</v>
       </c>
       <c r="B28" t="n">
-        <v>111153</v>
+        <v>8461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3488,37 +3488,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220240</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458920</v>
+        <v>458859</v>
       </c>
       <c r="R28" t="n">
-        <v>6781860</v>
+        <v>6781773</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3542,12 +3547,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3562,16 +3577,244 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298271</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135298272</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>458876</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6781809</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298272</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131674863</v>
+      </c>
+      <c r="B30" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>458920</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6781860</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131674863</t>
         </is>
@@ -3606,6 +3849,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6823-2026 artfynd.xlsx
+++ b/artfynd/A 6823-2026 artfynd.xlsx
@@ -3597,7 +3597,7 @@
         <v>135298272</v>
       </c>
       <c r="B29" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
